--- a/オーダー端末/PG実践Ⅱ_設計書（クラス仕様書、モジュール仕様書）.xlsx
+++ b/オーダー端末/PG実践Ⅱ_設計書（クラス仕様書、モジュール仕様書）.xlsx
@@ -1,39 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\oicsrv\教員個人\m-shimizu\Private\授業準備\2026年度\PG実践Ⅱ\教材\第1回\PG実践Ⅱ_第1回実践課題①-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shira\source\repos\OrderApp\オーダー端末\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7736A7C6-44D1-41B5-BF45-167EB250CB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A67847-F940-4A5D-A4D4-AC127EA43AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="24735" windowHeight="13980" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="721" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="クラス仕様書(○○)" sheetId="2" r:id="rId1"/>
-    <sheet name="モジュール仕様書（○○）" sheetId="4" r:id="rId2"/>
+    <sheet name="クラス仕様書(Kaikei)" sheetId="2" r:id="rId1"/>
+    <sheet name="モジュール仕様書（Kaikei）" sheetId="4" r:id="rId2"/>
+    <sheet name="モジュール仕様書（txtAzukariInput）" sheetId="5" r:id="rId3"/>
+    <sheet name="モジュール仕様書（UpdateDisplay）" sheetId="6" r:id="rId4"/>
+    <sheet name="モジュール仕様書（CashButton_Click） " sheetId="7" r:id="rId5"/>
+    <sheet name="モジュール仕様書（HakkouButton_Click）" sheetId="8" r:id="rId6"/>
+    <sheet name="モジュール仕様書（Button_Click）" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'クラス仕様書(○○)'!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'モジュール仕様書（○○）'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'クラス仕様書(Kaikei)'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'モジュール仕様書（Button_Click）'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'モジュール仕様書（CashButton_Click） '!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'モジュール仕様書（HakkouButton_Click）'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'モジュール仕様書（Kaikei）'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'モジュール仕様書（txtAzukariInput）'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'モジュール仕様書（UpdateDisplay）'!$1:$12</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="68">
   <si>
     <t>クラス仕様書</t>
     <rPh sb="3" eb="6">
@@ -193,6 +200,225 @@
     <rPh sb="2" eb="4">
       <t>ジッセン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>券売機システム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Kaikei</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="4">
+      <t>シンキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡邊</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_goukei</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_azukari</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_orderItems</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>List&lt;(string Name, int Price)&gt;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>商品合計金額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お預かり金額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>注文商品一覧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	Kaikei(int goukei, List&lt;(string, int)&gt; orderItems)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>txtAzukariInput_TextChanged</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UpdateDisplay</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CashButton_Click</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HakkouButton_Click</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Button_Click</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>画面初期化、合計金額表示、注文情報保持</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お預かり金額の入力変更時に差額計算を実行</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不足／おつりの表示更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現金投入画面へ切替、入力欄有効化</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>食券発券処理、ファイル出力、注意画面表示</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>画面を閉じる（戻る）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Kaikei.xaml.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会計画面の初期化処理</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>合計金額の表示
+注文一覧の保持
+お預かり入力欄の初期状態設定
+画面表示の初期更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>txtGoukei：合計金額表示</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>画面コンポーネントを初期化する
+合計金額を画面に表示する
+注文一覧を内部フィールドに保持する
+お預かり入力欄を無効化する
+差額表示を初期化する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_azukari：入力されたお預かり金額
+差額表示：UpdateDisplay により更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力欄の文字列を取得
+数値変換（失敗時は 0）
+内部フィールド _azukari に設定
+UpdateDisplay を呼び出し差額表示を更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_goukei：合計金額
+_azukari：お預かり金額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>txtSashihiki：不足／おつり金額表示
+lblSashihiki：表示ラベル（不足／おつり）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>差額 diff = _azukari - _goukei を計算
+_azukari &lt;= 0 → 不足表示（¥0）
+diff &lt; 0 → 不足表示（不足額）
+diff &gt;= 0 → おつり表示（差額）
+表示色を状態に応じて変更する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通常画面を非表示
+現金投入画面を表示
+入力欄を有効化</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通常画面を非表示
+現金投入画面を表示
+お預かり入力欄を有効化
+入力欄にフォーカスを設定</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不足チェック
+食券ファイル生成
+発券後注意画面への切替</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_goukei：合計金額
+_azukari：預かり金額
+_orderItems：注文一覧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>_azukari &lt; _goukei の場合はエラー表示
+食券番号を生成（RCPT＋日時）
+注文内容・金額をテキストファイルに出力
+発券後注意画面を表示
+メッセージを「お取り忘れにご注意ください」に変更</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会計画面を閉じる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Window.Close() を実行し画面を閉じる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>goukei：商品合計金額
+orderItems：注文商品一覧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力された金額を数値変換
+差額計算処理の呼び出し</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不足／おつりの計算
+表示色・文言の更新</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -254,7 +480,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="90">
+  <borders count="91">
     <border>
       <left/>
       <right/>
@@ -1425,13 +1651,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1525,10 +1764,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1559,6 +1798,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1594,13 +1836,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1723,7 +1965,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
@@ -1738,8 +1980,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1756,8 +1998,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2079,12 +2321,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.8125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -2093,30 +2335,30 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:10" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="86"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="87" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="87"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="93" t="s">
+      <c r="B2" s="89"/>
+      <c r="C2" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="96"/>
       <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2133,323 +2375,395 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+    <row r="3" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="91"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="12"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="68" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A5" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="77"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="77"/>
+      <c r="E5" s="78"/>
       <c r="F5" s="9"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A6" s="69"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="102"/>
       <c r="F6" s="13"/>
       <c r="G6" s="14"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="68" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A7" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="78" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="81"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="83"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="54" t="s">
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A8" s="71"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="84"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A9" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
-    </row>
-    <row r="10" spans="1:10" s="19" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="57"/>
+    </row>
+    <row r="10" spans="1:10" s="19" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="61" t="s">
+      <c r="E10" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="59" t="s">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="33"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="20">
+        <v>1</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="68"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="22">
+        <v>2</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>28</v>
+      </c>
       <c r="C12" s="34"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
+      <c r="D12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="35"/>
       <c r="J12" s="36"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="22"/>
-      <c r="B13" s="33"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="22">
+        <v>3</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" s="34"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="D13" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
       <c r="I13" s="35"/>
       <c r="J13" s="36"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A14" s="22"/>
       <c r="B14" s="33"/>
       <c r="C14" s="34"/>
       <c r="D14" s="23"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="45"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
       <c r="I14" s="35"/>
       <c r="J14" s="36"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="22"/>
       <c r="B15" s="33"/>
       <c r="C15" s="34"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="46"/>
       <c r="I15" s="35"/>
       <c r="J15" s="36"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A16" s="22"/>
       <c r="B16" s="33"/>
       <c r="C16" s="34"/>
       <c r="D16" s="23"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="45"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
       <c r="I16" s="35"/>
       <c r="J16" s="36"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A17" s="22"/>
       <c r="B17" s="33"/>
       <c r="C17" s="34"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E17" s="44"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="54"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A18" s="22"/>
       <c r="B18" s="33"/>
       <c r="C18" s="34"/>
       <c r="D18" s="23"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53"/>
-    </row>
-    <row r="19" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="54" t="s">
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
-    </row>
-    <row r="20" spans="1:10" s="19" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="57"/>
+    </row>
+    <row r="20" spans="1:10" s="19" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="61" t="s">
+      <c r="C20" s="59"/>
+      <c r="D20" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="59" t="s">
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="J20" s="60"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="33"/>
+      <c r="J20" s="61"/>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A21" s="22">
+        <v>1</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="C21" s="34"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="49"/>
       <c r="I21" s="35"/>
       <c r="J21" s="36"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="22"/>
-      <c r="B22" s="33"/>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="22">
+        <v>2</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>36</v>
+      </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
+      <c r="D22" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="35"/>
       <c r="J22" s="36"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="22"/>
-      <c r="B23" s="33"/>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A23" s="22">
+        <v>3</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>37</v>
+      </c>
       <c r="C23" s="34"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45"/>
+      <c r="D23" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
       <c r="I23" s="35"/>
       <c r="J23" s="36"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22"/>
-      <c r="B24" s="33"/>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A24" s="22">
+        <v>4</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>38</v>
+      </c>
       <c r="C24" s="34"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45"/>
+      <c r="D24" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="46"/>
       <c r="I24" s="35"/>
       <c r="J24" s="36"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="22"/>
-      <c r="B25" s="33"/>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A25" s="22">
+        <v>5</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="C25" s="34"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
+      <c r="D25" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
       <c r="I25" s="35"/>
       <c r="J25" s="36"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="22"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A26" s="22">
+        <v>6</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
       <c r="I26" s="35"/>
       <c r="J26" s="36"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A27" s="22"/>
       <c r="B27" s="33"/>
       <c r="C27" s="34"/>
@@ -2461,7 +2775,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="36"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A28" s="22"/>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
@@ -2473,7 +2787,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="36"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="22"/>
       <c r="B29" s="33"/>
       <c r="C29" s="34"/>
@@ -2485,7 +2799,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="36"/>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A30" s="22"/>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -2497,7 +2811,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="36"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A31" s="22"/>
       <c r="B31" s="33"/>
       <c r="C31" s="34"/>
@@ -2509,7 +2823,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="36"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A32" s="22"/>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -2521,7 +2835,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="36"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A33" s="24"/>
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
@@ -2630,7 +2944,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
@@ -2641,22 +2955,22 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="86"/>
-    </row>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="114" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2675,17 +2989,25 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="115"/>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
       <c r="B3" s="35"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="115"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
       <c r="B4" s="35"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -2693,19 +3015,21 @@
       <c r="F4" s="11"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="115" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="115"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
       <c r="B6" s="35"/>
       <c r="C6" s="13"/>
       <c r="D6" s="14"/>
@@ -2713,91 +3037,105 @@
       <c r="F6" s="15"/>
       <c r="G6" s="16"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" s="115" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" s="115"/>
+      <c r="D7" s="81" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
       <c r="B8" s="35"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="115" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="119"/>
-    </row>
-    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="104"/>
-    </row>
-    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="107"/>
-    </row>
-    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="110"/>
-    </row>
-    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="109" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="113"/>
+      <c r="B14" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2826,4 +3164,1111 @@
   </headerFooter>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021ADCF2-F314-4EAF-B1B1-5657059E6C2D}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="106"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:G10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;G</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B53130-FAC5-4C22-8109-924FD5D0DCCC}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="106" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:G10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;G</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB874E19-46D6-4FCE-B8F6-EC81C1451F94}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="106"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="109"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:G10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;G</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A96B445-4231-490C-8CC1-95694D0BF2A4}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="109"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:G10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;G</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CE2E7A-44CB-4F7D-8929-4D9C7BEBC7B9}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.4" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="116"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A4" s="116"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A5" s="116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="116"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="116"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="108"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+    </row>
+    <row r="14" spans="1:7" ht="240" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="114"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:G10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;G</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
 </file>